--- a/site/data/downloads/raw_data.xlsx
+++ b/site/data/downloads/raw_data.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="로우데이터" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="로우데이터" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/site/data/downloads/raw_data.xlsx
+++ b/site/data/downloads/raw_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1809"/>
+  <dimension ref="A1:F1810"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -47736,6 +47736,36 @@
         </is>
       </c>
     </row>
+    <row r="1810">
+      <c r="A1810" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B1810" t="inlineStr">
+        <is>
+          <t>미국</t>
+        </is>
+      </c>
+      <c r="C1810" t="inlineStr">
+        <is>
+          <t>정책금리(상단)</t>
+        </is>
+      </c>
+      <c r="D1810" t="n">
+        <v>4</v>
+      </c>
+      <c r="E1810" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="F1810" t="inlineStr">
+        <is>
+          <t>수시</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/site/data/downloads/raw_data.xlsx
+++ b/site/data/downloads/raw_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1810"/>
+  <dimension ref="A1:F1812"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -47766,6 +47766,66 @@
         </is>
       </c>
     </row>
+    <row r="1811">
+      <c r="A1811" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B1811" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C1811" t="inlineStr">
+        <is>
+          <t>CPI 헤드라인</t>
+        </is>
+      </c>
+      <c r="D1811" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="E1811" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="F1811" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
+    </row>
+    <row r="1812">
+      <c r="A1812" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B1812" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C1812" t="inlineStr">
+        <is>
+          <t>CPI 근원</t>
+        </is>
+      </c>
+      <c r="D1812" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="E1812" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="F1812" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/site/data/downloads/raw_data.xlsx
+++ b/site/data/downloads/raw_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1812"/>
+  <dimension ref="A1:F1813"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -47826,6 +47826,36 @@
         </is>
       </c>
     </row>
+    <row r="1813">
+      <c r="A1813" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B1813" t="inlineStr">
+        <is>
+          <t>미국</t>
+        </is>
+      </c>
+      <c r="C1813" t="inlineStr">
+        <is>
+          <t>PCE 근원</t>
+        </is>
+      </c>
+      <c r="D1813" t="n">
+        <v>3.0076</v>
+      </c>
+      <c r="E1813" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="F1813" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/site/data/downloads/raw_data.xlsx
+++ b/site/data/downloads/raw_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1813"/>
+  <dimension ref="A1:F1819"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -47856,6 +47856,161 @@
         </is>
       </c>
     </row>
+    <row r="1814">
+      <c r="A1814" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B1814" t="inlineStr">
+        <is>
+          <t>미국</t>
+        </is>
+      </c>
+      <c r="C1814" t="inlineStr">
+        <is>
+          <t>WTI</t>
+        </is>
+      </c>
+      <c r="D1814" t="n">
+        <v>97.31</v>
+      </c>
+      <c r="F1814" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
+    </row>
+    <row r="1815">
+      <c r="A1815" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B1815" t="inlineStr">
+        <is>
+          <t>미국</t>
+        </is>
+      </c>
+      <c r="C1815" t="inlineStr">
+        <is>
+          <t>국채10년</t>
+        </is>
+      </c>
+      <c r="D1815" t="n">
+        <v>4.99</v>
+      </c>
+      <c r="E1815" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="F1815" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
+    </row>
+    <row r="1816">
+      <c r="A1816" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B1816" t="inlineStr">
+        <is>
+          <t>독일</t>
+        </is>
+      </c>
+      <c r="C1816" t="inlineStr">
+        <is>
+          <t>실업률</t>
+        </is>
+      </c>
+      <c r="D1816" t="n">
+        <v>4</v>
+      </c>
+      <c r="F1816" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
+    </row>
+    <row r="1817">
+      <c r="A1817" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B1817" t="inlineStr">
+        <is>
+          <t>독일</t>
+        </is>
+      </c>
+      <c r="C1817" t="inlineStr">
+        <is>
+          <t>브렌트</t>
+        </is>
+      </c>
+      <c r="D1817" t="n">
+        <v>114.08</v>
+      </c>
+      <c r="F1817" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
+    </row>
+    <row r="1818">
+      <c r="A1818" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B1818" t="inlineStr">
+        <is>
+          <t>프랑스</t>
+        </is>
+      </c>
+      <c r="C1818" t="inlineStr">
+        <is>
+          <t>실업률</t>
+        </is>
+      </c>
+      <c r="D1818" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="F1818" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
+    </row>
+    <row r="1819">
+      <c r="A1819" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B1819" t="inlineStr">
+        <is>
+          <t>프랑스</t>
+        </is>
+      </c>
+      <c r="C1819" t="inlineStr">
+        <is>
+          <t>브렌트</t>
+        </is>
+      </c>
+      <c r="D1819" t="n">
+        <v>114.08</v>
+      </c>
+      <c r="F1819" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/site/data/downloads/raw_data.xlsx
+++ b/site/data/downloads/raw_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1819"/>
+  <dimension ref="A1:F1825"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -48011,6 +48011,166 @@
         </is>
       </c>
     </row>
+    <row r="1820">
+      <c r="A1820" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B1820" t="inlineStr">
+        <is>
+          <t>미국</t>
+        </is>
+      </c>
+      <c r="C1820" t="inlineStr">
+        <is>
+          <t>비농업고용</t>
+        </is>
+      </c>
+      <c r="D1820" t="n">
+        <v>159044</v>
+      </c>
+      <c r="E1820" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="F1820" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
+    </row>
+    <row r="1821">
+      <c r="A1821" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B1821" t="inlineStr">
+        <is>
+          <t>미국</t>
+        </is>
+      </c>
+      <c r="C1821" t="inlineStr">
+        <is>
+          <t>실업률</t>
+        </is>
+      </c>
+      <c r="D1821" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="E1821" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="F1821" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
+    </row>
+    <row r="1822">
+      <c r="A1822" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B1822" t="inlineStr">
+        <is>
+          <t>독일</t>
+        </is>
+      </c>
+      <c r="C1822" t="inlineStr">
+        <is>
+          <t>HICP 헤드라인</t>
+        </is>
+      </c>
+      <c r="D1822" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="F1822" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
+    </row>
+    <row r="1823">
+      <c r="A1823" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B1823" t="inlineStr">
+        <is>
+          <t>독일</t>
+        </is>
+      </c>
+      <c r="C1823" t="inlineStr">
+        <is>
+          <t>HICP 근원</t>
+        </is>
+      </c>
+      <c r="D1823" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F1823" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
+    </row>
+    <row r="1824">
+      <c r="A1824" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B1824" t="inlineStr">
+        <is>
+          <t>프랑스</t>
+        </is>
+      </c>
+      <c r="C1824" t="inlineStr">
+        <is>
+          <t>HICP 헤드라인</t>
+        </is>
+      </c>
+      <c r="D1824" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="F1824" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
+    </row>
+    <row r="1825">
+      <c r="A1825" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B1825" t="inlineStr">
+        <is>
+          <t>프랑스</t>
+        </is>
+      </c>
+      <c r="C1825" t="inlineStr">
+        <is>
+          <t>HICP 근원</t>
+        </is>
+      </c>
+      <c r="D1825" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="F1825" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/site/data/downloads/raw_data.xlsx
+++ b/site/data/downloads/raw_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1825"/>
+  <dimension ref="A1:F1827"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -48171,6 +48171,66 @@
         </is>
       </c>
     </row>
+    <row r="1826">
+      <c r="A1826" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B1826" t="inlineStr">
+        <is>
+          <t>한국</t>
+        </is>
+      </c>
+      <c r="C1826" t="inlineStr">
+        <is>
+          <t>CPI 헤드라인</t>
+        </is>
+      </c>
+      <c r="D1826" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="E1826" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="F1826" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
+    </row>
+    <row r="1827">
+      <c r="A1827" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B1827" t="inlineStr">
+        <is>
+          <t>한국</t>
+        </is>
+      </c>
+      <c r="C1827" t="inlineStr">
+        <is>
+          <t>CPI 근원</t>
+        </is>
+      </c>
+      <c r="D1827" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="E1827" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="F1827" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/site/data/downloads/raw_data.xlsx
+++ b/site/data/downloads/raw_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1827"/>
+  <dimension ref="A1:F1829"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -48231,6 +48231,56 @@
         </is>
       </c>
     </row>
+    <row r="1828">
+      <c r="A1828" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B1828" t="inlineStr">
+        <is>
+          <t>한국</t>
+        </is>
+      </c>
+      <c r="C1828" t="inlineStr">
+        <is>
+          <t>국채10년</t>
+        </is>
+      </c>
+      <c r="D1828" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="F1828" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
+    </row>
+    <row r="1829">
+      <c r="A1829" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B1829" t="inlineStr">
+        <is>
+          <t>한국</t>
+        </is>
+      </c>
+      <c r="C1829" t="inlineStr">
+        <is>
+          <t>국채10년</t>
+        </is>
+      </c>
+      <c r="D1829" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="F1829" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/site/data/downloads/raw_data.xlsx
+++ b/site/data/downloads/raw_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1829"/>
+  <dimension ref="A1:F1831"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -48281,6 +48281,56 @@
         </is>
       </c>
     </row>
+    <row r="1830">
+      <c r="A1830" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B1830" t="inlineStr">
+        <is>
+          <t>독일</t>
+        </is>
+      </c>
+      <c r="C1830" t="inlineStr">
+        <is>
+          <t>국채10년</t>
+        </is>
+      </c>
+      <c r="D1830" t="n">
+        <v>3.47</v>
+      </c>
+      <c r="F1830" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
+    </row>
+    <row r="1831">
+      <c r="A1831" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B1831" t="inlineStr">
+        <is>
+          <t>프랑스</t>
+        </is>
+      </c>
+      <c r="C1831" t="inlineStr">
+        <is>
+          <t>국채10년</t>
+        </is>
+      </c>
+      <c r="D1831" t="n">
+        <v>4.44</v>
+      </c>
+      <c r="F1831" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/site/data/downloads/raw_data.xlsx
+++ b/site/data/downloads/raw_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1831"/>
+  <dimension ref="A1:F1833"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -48331,6 +48331,66 @@
         </is>
       </c>
     </row>
+    <row r="1832">
+      <c r="A1832" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B1832" t="inlineStr">
+        <is>
+          <t>미국</t>
+        </is>
+      </c>
+      <c r="C1832" t="inlineStr">
+        <is>
+          <t>CPI 헤드라인</t>
+        </is>
+      </c>
+      <c r="D1832" t="n">
+        <v>3.7172</v>
+      </c>
+      <c r="E1832" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="F1832" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
+    </row>
+    <row r="1833">
+      <c r="A1833" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B1833" t="inlineStr">
+        <is>
+          <t>미국</t>
+        </is>
+      </c>
+      <c r="C1833" t="inlineStr">
+        <is>
+          <t>CPI 근원</t>
+        </is>
+      </c>
+      <c r="D1833" t="n">
+        <v>2.5658</v>
+      </c>
+      <c r="E1833" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="F1833" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/site/data/downloads/raw_data.xlsx
+++ b/site/data/downloads/raw_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1833"/>
+  <dimension ref="A1:F1835"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -48391,6 +48391,61 @@
         </is>
       </c>
     </row>
+    <row r="1834">
+      <c r="A1834" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B1834" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C1834" t="inlineStr">
+        <is>
+          <t>실업률</t>
+        </is>
+      </c>
+      <c r="D1834" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="E1834" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="F1834" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
+    </row>
+    <row r="1835">
+      <c r="A1835" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B1835" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C1835" t="inlineStr">
+        <is>
+          <t>국채10년</t>
+        </is>
+      </c>
+      <c r="D1835" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="F1835" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/site/data/downloads/raw_data.xlsx
+++ b/site/data/downloads/raw_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1835"/>
+  <dimension ref="A1:F1837"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -48410,11 +48410,6 @@
       <c r="D1834" t="n">
         <v>2.5</v>
       </c>
-      <c r="E1834" t="inlineStr">
-        <is>
-          <t>2026-10-02</t>
-        </is>
-      </c>
       <c r="F1834" t="inlineStr">
         <is>
           <t>월간</t>
@@ -48441,6 +48436,66 @@
         <v>3.05</v>
       </c>
       <c r="F1835" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
+    </row>
+    <row r="1836">
+      <c r="A1836" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B1836" t="inlineStr">
+        <is>
+          <t>한국</t>
+        </is>
+      </c>
+      <c r="C1836" t="inlineStr">
+        <is>
+          <t>취업자수</t>
+        </is>
+      </c>
+      <c r="D1836" t="n">
+        <v>29266</v>
+      </c>
+      <c r="E1836" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="F1836" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
+    </row>
+    <row r="1837">
+      <c r="A1837" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B1837" t="inlineStr">
+        <is>
+          <t>한국</t>
+        </is>
+      </c>
+      <c r="C1837" t="inlineStr">
+        <is>
+          <t>실업률</t>
+        </is>
+      </c>
+      <c r="D1837" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="E1837" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="F1837" t="inlineStr">
         <is>
           <t>월간</t>
         </is>

--- a/site/data/downloads/raw_data.xlsx
+++ b/site/data/downloads/raw_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1837"/>
+  <dimension ref="A1:F1843"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -48501,6 +48501,166 @@
         </is>
       </c>
     </row>
+    <row r="1838">
+      <c r="A1838" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B1838" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C1838" t="inlineStr">
+        <is>
+          <t>CPI 헤드라인</t>
+        </is>
+      </c>
+      <c r="D1838" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="E1838" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="F1838" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
+    </row>
+    <row r="1839">
+      <c r="A1839" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B1839" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C1839" t="inlineStr">
+        <is>
+          <t>CPI 근원</t>
+        </is>
+      </c>
+      <c r="D1839" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="E1839" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="F1839" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
+    </row>
+    <row r="1840">
+      <c r="A1840" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B1840" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C1840" t="inlineStr">
+        <is>
+          <t>두바이유</t>
+        </is>
+      </c>
+      <c r="D1840" t="n">
+        <v>88.05329999999999</v>
+      </c>
+      <c r="F1840" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
+    </row>
+    <row r="1841">
+      <c r="A1841" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B1841" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C1841" t="inlineStr">
+        <is>
+          <t>두바이유</t>
+        </is>
+      </c>
+      <c r="D1841" t="n">
+        <v>111.8252</v>
+      </c>
+      <c r="F1841" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
+    </row>
+    <row r="1842">
+      <c r="A1842" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B1842" t="inlineStr">
+        <is>
+          <t>한국</t>
+        </is>
+      </c>
+      <c r="C1842" t="inlineStr">
+        <is>
+          <t>두바이유</t>
+        </is>
+      </c>
+      <c r="D1842" t="n">
+        <v>88.05329999999999</v>
+      </c>
+      <c r="F1842" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
+    </row>
+    <row r="1843">
+      <c r="A1843" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B1843" t="inlineStr">
+        <is>
+          <t>한국</t>
+        </is>
+      </c>
+      <c r="C1843" t="inlineStr">
+        <is>
+          <t>두바이유</t>
+        </is>
+      </c>
+      <c r="D1843" t="n">
+        <v>111.8252</v>
+      </c>
+      <c r="F1843" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/site/data/downloads/raw_data.xlsx
+++ b/site/data/downloads/raw_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1843"/>
+  <dimension ref="A1:F1844"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -48661,6 +48661,36 @@
         </is>
       </c>
     </row>
+    <row r="1844">
+      <c r="A1844" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B1844" t="inlineStr">
+        <is>
+          <t>한국</t>
+        </is>
+      </c>
+      <c r="C1844" t="inlineStr">
+        <is>
+          <t>실질GDP 성장률</t>
+        </is>
+      </c>
+      <c r="D1844" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="E1844" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="F1844" t="inlineStr">
+        <is>
+          <t>분기</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/site/data/downloads/raw_data.xlsx
+++ b/site/data/downloads/raw_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1844"/>
+  <dimension ref="A1:F1846"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -48691,6 +48691,66 @@
         </is>
       </c>
     </row>
+    <row r="1845">
+      <c r="A1845" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B1845" t="inlineStr">
+        <is>
+          <t>미국</t>
+        </is>
+      </c>
+      <c r="C1845" t="inlineStr">
+        <is>
+          <t>PCE 근원</t>
+        </is>
+      </c>
+      <c r="D1845" t="n">
+        <v>3.1212</v>
+      </c>
+      <c r="E1845" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="F1845" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
+    </row>
+    <row r="1846">
+      <c r="A1846" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B1846" t="inlineStr">
+        <is>
+          <t>미국</t>
+        </is>
+      </c>
+      <c r="C1846" t="inlineStr">
+        <is>
+          <t>실질GDP 성장률</t>
+        </is>
+      </c>
+      <c r="D1846" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="E1846" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="F1846" t="inlineStr">
+        <is>
+          <t>분기</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/site/data/downloads/raw_data.xlsx
+++ b/site/data/downloads/raw_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1846"/>
+  <dimension ref="A1:F1850"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -48751,6 +48751,106 @@
         </is>
       </c>
     </row>
+    <row r="1847">
+      <c r="A1847" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B1847" t="inlineStr">
+        <is>
+          <t>독일</t>
+        </is>
+      </c>
+      <c r="C1847" t="inlineStr">
+        <is>
+          <t>실업률</t>
+        </is>
+      </c>
+      <c r="D1847" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="F1847" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
+    </row>
+    <row r="1848">
+      <c r="A1848" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B1848" t="inlineStr">
+        <is>
+          <t>독일</t>
+        </is>
+      </c>
+      <c r="C1848" t="inlineStr">
+        <is>
+          <t>실질GDP 성장률</t>
+        </is>
+      </c>
+      <c r="D1848" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F1848" t="inlineStr">
+        <is>
+          <t>분기</t>
+        </is>
+      </c>
+    </row>
+    <row r="1849">
+      <c r="A1849" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B1849" t="inlineStr">
+        <is>
+          <t>프랑스</t>
+        </is>
+      </c>
+      <c r="C1849" t="inlineStr">
+        <is>
+          <t>실업률</t>
+        </is>
+      </c>
+      <c r="D1849" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="F1849" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
+    </row>
+    <row r="1850">
+      <c r="A1850" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B1850" t="inlineStr">
+        <is>
+          <t>프랑스</t>
+        </is>
+      </c>
+      <c r="C1850" t="inlineStr">
+        <is>
+          <t>실질GDP 성장률</t>
+        </is>
+      </c>
+      <c r="D1850" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="F1850" t="inlineStr">
+        <is>
+          <t>분기</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
